--- a/src/main/resources/orchestrator.xlsx
+++ b/src/main/resources/orchestrator.xlsx
@@ -485,17 +485,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/irisCalls/{model}/{colorId}/{promoCode}</t>
+          <t>/providerCalls/{model}/{colorId}/{promoCode}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>irisCall-orchestrator</t>
+          <t>providerCall-orchestrator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>irisCallLookupPlan</t>
+          <t>providerCallLookupPlan</t>
         </is>
       </c>
     </row>
@@ -523,17 +523,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/irisCalls-enriched/{model}/{colorId}/{promoCode}</t>
+          <t>/providerCalls-enriched/{model}/{colorId}/{promoCode}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>irisCall-orchestrator</t>
+          <t>providerCall-orchestrator</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>irisCallEnrichmentPlan</t>
+          <t>providerCallEnrichmentPlan</t>
         </is>
       </c>
     </row>
@@ -561,17 +561,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/irisCallAccumulated/{model}</t>
+          <t>/providerCallAccumulated/{model}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>irisCallAccumulated-orchestrator</t>
+          <t>providerCallAccumulated-orchestrator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>irisCallAccumulatedPlan</t>
+          <t>providerCallAccumulatedPlan</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>step_irisCall</t>
+          <t>step_order</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>irisCallLookupPlan</t>
+          <t>providerCallLookupPlan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>irisCallEnrichmentPlan</t>
+          <t>providerCallEnrichmentPlan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>irisCallEnrichmentPlan</t>
+          <t>providerCallEnrichmentPlan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>irisCallAccumulatedPlan</t>
+          <t>providerCallAccumulatedPlan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>irisCallAccumulated</t>
+          <t>providerCallAccumulated</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -802,12 +802,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>/demo-api/irisCallAccumulated/{model}</t>
+          <t>/demo-api/providerCallAccumulated/{model}</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>irisCallAccumulatedRequest</t>
+          <t>providerCallAccumulatedRequest</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -956,7 +956,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>irisCallAccumulatedRequest</t>
+          <t>providerCallAccumulatedRequest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>irisCallLookupPlan</t>
+          <t>providerCallLookupPlan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>irisCall</t>
+          <t>providerCall</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>irisCallEnrichmentPlan</t>
+          <t>providerCallEnrichmentPlan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>irisCall</t>
+          <t>providerCall</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>irisCallEnrichmentPlan</t>
+          <t>providerCallEnrichmentPlan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>irisCallAccumulatedPlan</t>
+          <t>providerCallAccumulatedPlan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>irisCallAccumulated</t>
+          <t>providerCallAccumulated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$.steps.irisCallAccumulated</t>
+          <t>$.steps.providerCallAccumulated</t>
         </is>
       </c>
       <c r="E5" t="b">
